--- a/inventory/files/2026-W40/Q4_ship_plan_2026-W40.xlsx
+++ b/inventory/files/2026-W40/Q4_ship_plan_2026-W40.xlsx
@@ -450,7 +450,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q4 shipment files, 2026-W40 (as of 2026-10-08)</t>
+          <t>Q4 shipment files, 2026-W40 (as of 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>100035</v>
+        <v>98787</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
@@ -524,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>3956</v>
+        <v>3780</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
@@ -545,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>14816</v>
+        <v>14748</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
@@ -566,7 +566,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4125</v>
+        <v>4108</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -587,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -650,7 +650,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>4910</v>
+        <v>4889</v>
       </c>
       <c r="E14" t="n">
         <v>9</v>
@@ -713,7 +713,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E15" t="n">
         <v>39</v>
@@ -734,7 +734,7 @@
         <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="E16" t="n">
         <v>28</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J2" t="n">
         <v>24</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>16.6</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
         <v>16</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="J7" t="n">
         <v>22</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>90.7</v>
+        <v>91.7</v>
       </c>
       <c r="J8" t="n">
         <v>36</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2825</v>
+        <v>2817</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2825</v>
+        <v>2817</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="J2" t="n">
         <v>1355</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J3" t="n">
         <v>85</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
         <v>45</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>20.2</v>
+        <v>21.7</v>
       </c>
       <c r="J5" t="n">
         <v>134</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="J6" t="n">
         <v>557</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="J7" t="n">
         <v>182</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>99.40000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="J10" t="n">
         <v>49</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="J2" t="n">
         <v>88</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
         <v>19</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="J5" t="n">
         <v>37</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="J13" t="n">
         <v>46</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
         <v>94</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="J3" t="n">
         <v>96</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>15</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="J10" t="n">
         <v>150</v>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="J14" t="n">
         <v>73</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="J16" t="n">
         <v>24</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="J20" t="n">
         <v>24</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
       <c r="J24" t="n">
         <v>33</v>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -6147,13 +6147,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72240</v>
+        <v>71820</v>
       </c>
       <c r="C2" t="n">
         <v>105</v>
       </c>
       <c r="D2" t="n">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>72138</v>
+        <v>71746</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J2" t="n">
         <v>22724</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6828</v>
+        <v>6742</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6828</v>
+        <v>6742</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>868</v>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5433</v>
+        <v>5211</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5433</v>
+        <v>5211</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="J4" t="n">
         <v>4448</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4294</v>
+        <v>4066</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4294</v>
+        <v>4066</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>2398</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2360</v>
+        <v>2326</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="J6" t="n">
         <v>1826</v>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1790</v>
+        <v>1735</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1790</v>
+        <v>1735</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6507,13 +6507,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="C8" t="n">
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="J9" t="n">
         <v>109</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6631,30 +6631,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-MICRTOWEL12A</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>840</v>
-      </c>
-      <c r="C10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" t="n">
-        <v>21</v>
+        <v>762</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B0DJMW6283</t>
+          <t>B0FW6WFX4D</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Microfiber Towels for Cars</t>
+          <t>Rapid Ceramic Wheel Sealant Spray</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>822</v>
+        <v>762</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -6662,22 +6656,22 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>48.8</v>
+        <v>13.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2435</v>
+        <v>370</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Seller Central case pack 2026-09-28</t>
+          <t>MISSING: NIC to add units per box</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -6695,24 +6689,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-MICRTOWEL12A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>777</v>
+        <v>760</v>
+      </c>
+      <c r="C11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B0FW6WFX4D</t>
+          <t>B0DJMW6283</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Wheel Sealant Spray</t>
+          <t>Microfiber Towels for Cars</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>777</v>
+        <v>754</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -6720,22 +6720,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>49.7</v>
       </c>
       <c r="J11" t="n">
-        <v>370</v>
+        <v>2435</v>
       </c>
       <c r="K11" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="J12" t="n">
         <v>348</v>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="J14" t="n">
         <v>469</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="J15" t="n">
         <v>252</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7043,30 +7043,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AH-813A</t>
+          <t>AH-RCINT14-2PA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B0F3G1V5SF</t>
+          <t>B0DKVBTNNT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ceramic Glass Coat Pro Pack</t>
+          <t>Rapid Ceramic Interior Detailer and Protectant Spray</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -7074,17 +7074,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="J17" t="n">
-        <v>178</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7107,61 +7107,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AH-RCINT14-2PA</t>
+          <t>AH-RCPAINTQA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>144</v>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B0DKVBTNNT</t>
+          <t>B0C4ZVMRRK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Interior Detailer and Protectant Spray</t>
+          <t>Rapid Ceramic Paint Sealant</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>BELOW_TARGET</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>13.3</v>
+        <v>63.8</v>
       </c>
       <c r="J18" t="n">
-        <v>42</v>
+        <v>1214</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Seller Central case pack 2026-09-28</t>
+          <t>MISSING: NIC to add units per box</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>top FBA SKU by 30-day FBA units</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>AH-RCPAINT-QA, AH-RCPAINT-QAUPC, AHW-104QA</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>US</t>
@@ -7171,59 +7169,61 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AH-RCPAINTQA</t>
+          <t>AH-813A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>144</v>
+        <v>120</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B0C4ZVMRRK</t>
+          <t>B0F3G1V5SF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Paint Sealant</t>
+          <t>Ceramic Glass Coat Pro Pack</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BELOW_TARGET</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>62.9</v>
+        <v>14.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1214</v>
+        <v>178</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>top FBA SKU by 30-day FBA units</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>AH-RCPAINT-QA, AH-RCPAINT-QAUPC, AHW-104QA</t>
-        </is>
-      </c>
+          <t>only FBA SKU</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>US</t>
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>36.1</v>
+        <v>36.7</v>
       </c>
       <c r="J20" t="n">
         <v>277</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="J21" t="n">
         <v>68</v>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>59.8</v>
+        <v>61.5</v>
       </c>
       <c r="J22" t="n">
         <v>655</v>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
         <v>30</v>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>63.4</v>
+        <v>64.7</v>
       </c>
       <c r="J24" t="n">
         <v>269</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1657</v>
+        <v>1628</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1657</v>
+        <v>1628</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -7979,7 +7979,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>795</v>
+        <v>686</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>795</v>
+        <v>686</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="J4" t="n">
         <v>7476</v>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>18.4</v>
+        <v>19.2</v>
       </c>
       <c r="J5" t="n">
         <v>520</v>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="J6" t="n">
         <v>110</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12558</v>
+        <v>12521</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12558</v>
+        <v>12521</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="J2" t="n">
         <v>3108</v>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>40.8</v>
+        <v>41.4</v>
       </c>
       <c r="J3" t="n">
         <v>1044</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="J4" t="n">
         <v>202</v>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>42.2</v>
+        <v>44.1</v>
       </c>
       <c r="J5" t="n">
         <v>256</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="J6" t="n">
         <v>133</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="J7" t="n">
         <v>134</v>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2372</v>
+        <v>2353</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2372</v>
+        <v>2353</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>57.6</v>
+        <v>60.3</v>
       </c>
       <c r="J2" t="n">
         <v>279</v>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>105.4</v>
+        <v>105.6</v>
       </c>
       <c r="J2" t="n">
         <v>3586</v>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>91.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>76</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>64.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>76</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
